--- a/data/gravel/Otso Fenrir Ti (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Ti (long) 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3AB376-98C5-4441-95F4-3F5DCCD1FE34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738CBAB3-B0DE-5540-B829-FDE6DAFE3F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31880" yWindow="-24300" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="151">
   <si>
     <t>brand</t>
   </si>
@@ -490,6 +490,24 @@
   </si>
   <si>
     <t>Fenrir Ti (long)</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -841,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1805,174 +1823,204 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55">
-        <v>40</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>55</v>
+      </c>
+      <c r="B61">
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>76</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>68</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>70</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B71">
-        <v>3750</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>72</v>
-      </c>
-      <c r="B72">
-        <v>5410</v>
+        <v>66</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>69</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B77">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78">
+        <v>5410</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
         <v>84</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>85</v>
       </c>
     </row>

--- a/data/gravel/Otso Fenrir Ti (long) 2025.xlsx
+++ b/data/gravel/Otso Fenrir Ti (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738CBAB3-B0DE-5540-B829-FDE6DAFE3F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9540861-E4B1-5041-ABFF-A9F85B5D2A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31880" yWindow="-24300" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="153">
   <si>
     <t>brand</t>
   </si>
@@ -417,9 +417,6 @@
     <t>±0.2°</t>
   </si>
   <si>
-    <t>Fork Axle to Crown Length (mm)</t>
-  </si>
-  <si>
     <t>Geometry Parameter</t>
   </si>
   <si>
@@ -477,9 +474,6 @@
     <t>internal</t>
   </si>
   <si>
-    <t>a8:g34</t>
-  </si>
-  <si>
     <t>2.6 at long</t>
   </si>
   <si>
@@ -508,6 +502,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>Rigid Fork Axle to Crown Length (mm)</t>
+  </si>
+  <si>
+    <t>a8:g36</t>
   </si>
 </sst>
 </file>
@@ -859,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -879,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -916,7 +922,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
@@ -967,7 +973,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>116</v>
@@ -1052,16 +1058,16 @@
         <v>119</v>
       </c>
       <c r="M12" t="s">
+        <v>120</v>
+      </c>
+      <c r="N12" t="s">
         <v>121</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>122</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>123</v>
-      </c>
-      <c r="P12" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
@@ -1096,12 +1102,12 @@
         <v>450</v>
       </c>
       <c r="P13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>117</v>
@@ -1131,7 +1137,7 @@
         <v>72</v>
       </c>
       <c r="P14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
@@ -1192,7 +1198,7 @@
         <v>67.8</v>
       </c>
       <c r="P16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
@@ -1247,7 +1253,7 @@
         <v>74.8</v>
       </c>
       <c r="P17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
@@ -1296,14 +1302,14 @@
         <v>107</v>
       </c>
       <c r="N18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O18" t="e" cm="1">
         <f t="array" ref="O18">+≈20 mm</f>
         <v>#NAME?</v>
       </c>
       <c r="P18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
@@ -1395,24 +1401,24 @@
         <v>51</v>
       </c>
       <c r="M21" t="s">
+        <v>132</v>
+      </c>
+      <c r="N21" t="s">
         <v>133</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>134</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>135</v>
-      </c>
-      <c r="P21" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>120</v>
+      <c r="B22" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="C22">
         <v>495</v>
@@ -1433,13 +1439,13 @@
         <v>106</v>
       </c>
       <c r="N22" t="s">
+        <v>129</v>
+      </c>
+      <c r="O22" t="s">
         <v>130</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>131</v>
-      </c>
-      <c r="P22" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -1512,460 +1518,484 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>29</v>
+      <c r="A26" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>30</v>
+      <c r="A27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29">
-        <v>1814</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30">
-        <v>29</v>
-      </c>
-      <c r="D30">
-        <v>29</v>
-      </c>
-      <c r="E30">
-        <v>29</v>
-      </c>
-      <c r="F30">
-        <v>29</v>
-      </c>
-      <c r="G30">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31">
-        <v>2.35</v>
-      </c>
-      <c r="D31">
-        <v>2.35</v>
-      </c>
-      <c r="E31">
-        <v>2.35</v>
+        <v>32</v>
       </c>
       <c r="F31">
-        <v>2.35</v>
-      </c>
-      <c r="G31">
-        <v>2.35</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32">
-        <v>2.2999999999999998</v>
+        <v>29</v>
       </c>
       <c r="D32">
-        <v>2.2999999999999998</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>2.2999999999999998</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>2.2999999999999998</v>
+        <v>29</v>
       </c>
       <c r="G32">
-        <v>2.2999999999999998</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>2.35</v>
+      </c>
+      <c r="D33">
+        <v>2.35</v>
+      </c>
+      <c r="E33">
+        <v>2.35</v>
+      </c>
+      <c r="F33">
+        <v>2.35</v>
+      </c>
+      <c r="G33">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F34">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G34">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="C33">
-        <f>C35*2.54</f>
+      <c r="C35">
+        <f>C37*2.54</f>
         <v>147.32</v>
       </c>
-      <c r="D33">
-        <f t="shared" ref="D33:G34" si="5">D35*2.54</f>
+      <c r="D35">
+        <f t="shared" ref="D35:G36" si="5">D37*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <f t="shared" si="5"/>
         <v>170.18</v>
       </c>
-      <c r="F33">
+      <c r="F35">
         <f t="shared" si="5"/>
         <v>177.8</v>
       </c>
-      <c r="G33">
+      <c r="G35">
         <f t="shared" si="5"/>
         <v>190.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>37</v>
       </c>
-      <c r="C34">
-        <f>C36*2.54</f>
+      <c r="C36">
+        <f>C38*2.54</f>
         <v>162.56</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <f t="shared" si="5"/>
         <v>170.18</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <f t="shared" si="5"/>
         <v>180.34</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <f t="shared" si="5"/>
         <v>190.5</v>
       </c>
-      <c r="G34">
+      <c r="G36">
         <f t="shared" si="5"/>
         <v>198.12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="C35" s="2">
+    <row r="37" spans="1:8" ht="22" x14ac:dyDescent="0.3">
+      <c r="C37" s="2">
         <v>58</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D37" s="2">
         <v>63</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E37" s="2">
         <v>67</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F37" s="2">
         <v>70</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G37" s="2">
         <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36">
-        <v>64</v>
-      </c>
-      <c r="D36">
-        <v>67</v>
-      </c>
-      <c r="E36">
-        <v>71</v>
-      </c>
-      <c r="F36">
-        <v>75</v>
-      </c>
-      <c r="G36">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>77</v>
-      </c>
-      <c r="B37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" t="s">
-        <v>91</v>
-      </c>
-      <c r="D37" t="s">
-        <v>92</v>
-      </c>
-      <c r="E37" t="s">
-        <v>93</v>
-      </c>
-      <c r="F37" t="s">
-        <v>94</v>
-      </c>
-      <c r="G37" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>82</v>
+        <v>38</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38">
+        <v>64</v>
+      </c>
+      <c r="D38">
+        <v>67</v>
+      </c>
+      <c r="E38">
+        <v>71</v>
+      </c>
+      <c r="F38">
+        <v>75</v>
+      </c>
+      <c r="G38">
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" t="s">
+        <v>95</v>
+      </c>
+      <c r="H39" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43">
-        <v>2.6</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>141</v>
+        <v>41</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B44">
-        <v>2.8</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>142</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B45">
-        <v>120</v>
+        <v>2.6</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>2.8</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B48" s="1"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49">
-        <v>148</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50">
-        <v>110</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>146</v>
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59">
-        <v>31.6</v>
+        <v>51</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B61">
-        <v>40</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>40</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>76</v>
@@ -1973,7 +2003,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
@@ -1981,7 +2011,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
@@ -1989,38 +2019,54 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>71</v>
-      </c>
-      <c r="B77">
-        <v>3750</v>
+        <v>69</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>72</v>
-      </c>
-      <c r="B78">
-        <v>5410</v>
+        <v>70</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B79">
+        <v>3750</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
+      </c>
+      <c r="B80">
+        <v>5410</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
         <v>84</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B83" t="s">
         <v>85</v>
       </c>
     </row>
